--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:25:29+00:00</t>
+    <t>2024-10-26T11:41:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:41:35+00:00</t>
+    <t>2024-10-26T12:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:52:52+00:00</t>
+    <t>2024-10-26T13:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9385" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9461" uniqueCount="978">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:45:19+00:00</t>
+    <t>2024-10-26T13:53:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1974,6 +1974,22 @@
     <t>Patient.address.extension</t>
   </si>
   <si>
+    <t>Patient.address.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>municipalityCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Code</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+  </si>
+  <si>
     <t>Patient.address.use</t>
   </si>
   <si>
@@ -2680,6 +2696,9 @@
   </si>
   <si>
     <t>Patient.contact.address.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.address.extension:municipalityCode</t>
   </si>
   <si>
     <t>Patient.contact.address.use</t>
@@ -3321,7 +3340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP246"/>
+  <dimension ref="A1:AP248"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.9765625" customWidth="true" bestFit="true"/>
@@ -19936,9 +19955,11 @@
         <v>635</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>634</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
       </c>
@@ -19953,26 +19974,22 @@
         <v>21</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>110</v>
+        <v>637</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O139" t="s" s="2">
         <v>639</v>
       </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>21</v>
       </c>
@@ -19984,7 +20001,7 @@
         <v>21</v>
       </c>
       <c r="T139" t="s" s="2">
-        <v>640</v>
+        <v>21</v>
       </c>
       <c r="U139" t="s" s="2">
         <v>21</v>
@@ -19996,13 +20013,13 @@
         <v>21</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>641</v>
+        <v>21</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>642</v>
+        <v>21</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>21</v>
@@ -20020,25 +20037,25 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>643</v>
+        <v>161</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>644</v>
+        <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>21</v>
@@ -20047,7 +20064,7 @@
         <v>21</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>645</v>
+        <v>21</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>21</v>
@@ -20055,10 +20072,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20075,7 +20092,7 @@
         <v>21</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>91</v>
@@ -20084,15 +20101,17 @@
         <v>110</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>21</v>
       </c>
@@ -20104,7 +20123,7 @@
         <v>21</v>
       </c>
       <c r="T140" t="s" s="2">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="U140" t="s" s="2">
         <v>21</v>
@@ -20119,10 +20138,10 @@
         <v>227</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>21</v>
@@ -20140,7 +20159,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20155,7 +20174,7 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>21</v>
+        <v>649</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>475</v>
@@ -20167,7 +20186,7 @@
         <v>21</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>21</v>
@@ -20175,10 +20194,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20201,20 +20220,18 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>654</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>21</v>
       </c>
@@ -20226,7 +20243,7 @@
         <v>21</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>21</v>
@@ -20238,13 +20255,13 @@
         <v>21</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>21</v>
+        <v>656</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>21</v>
@@ -20262,7 +20279,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -20277,10 +20294,10 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>661</v>
+        <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>21</v>
@@ -20289,7 +20306,7 @@
         <v>21</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>21</v>
@@ -20297,10 +20314,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20311,7 +20328,7 @@
         <v>81</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>21</v>
@@ -20326,13 +20343,17 @@
         <v>219</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
       </c>
@@ -20344,7 +20365,7 @@
         <v>21</v>
       </c>
       <c r="T142" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="U142" t="s" s="2">
         <v>21</v>
@@ -20380,13 +20401,13 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>21</v>
@@ -20395,10 +20416,10 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>669</v>
+        <v>483</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>21</v>
@@ -20407,7 +20428,7 @@
         <v>21</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>21</v>
@@ -20415,10 +20436,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20429,7 +20450,7 @@
         <v>81</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>21</v>
@@ -20438,16 +20459,16 @@
         <v>21</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>219</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>585</v>
+        <v>669</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>586</v>
+        <v>670</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -20462,7 +20483,7 @@
         <v>21</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>21</v>
+        <v>671</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>21</v>
@@ -20498,25 +20519,25 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>151</v>
+        <v>672</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>21</v>
+        <v>673</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>21</v>
+        <v>674</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>21</v>
@@ -20525,7 +20546,7 @@
         <v>21</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>21</v>
+        <v>675</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>21</v>
@@ -20533,10 +20554,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20547,7 +20568,7 @@
         <v>81</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>21</v>
@@ -20559,13 +20580,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>136</v>
+        <v>585</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>137</v>
+        <v>586</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20604,29 +20625,31 @@
         <v>21</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC144" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>21</v>
@@ -20649,14 +20672,12 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>21</v>
       </c>
@@ -20665,7 +20686,7 @@
         <v>81</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>21</v>
@@ -20677,13 +20698,13 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>675</v>
+        <v>135</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>676</v>
+        <v>136</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>677</v>
+        <v>137</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20722,16 +20743,14 @@
         <v>21</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC145" s="2"/>
       <c r="AD145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF145" t="s" s="2">
         <v>161</v>
@@ -20752,7 +20771,7 @@
         <v>21</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>678</v>
+        <v>21</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>21</v>
@@ -20769,13 +20788,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C146" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>21</v>
@@ -20797,13 +20816,13 @@
         <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20872,7 +20891,7 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>21</v>
@@ -20889,13 +20908,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C147" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>21</v>
@@ -20917,10 +20936,10 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="M147" t="s" s="2">
         <v>688</v>
@@ -21012,7 +21031,7 @@
         <v>690</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>691</v>
@@ -21043,7 +21062,7 @@
         <v>693</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -21103,7 +21122,7 @@
         <v>82</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>141</v>
@@ -21112,7 +21131,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>21</v>
+        <v>694</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -21132,9 +21151,11 @@
         <v>695</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C149" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="D149" t="s" s="2">
         <v>21</v>
       </c>
@@ -21155,13 +21176,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>219</v>
+        <v>697</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21185,7 +21206,7 @@
         <v>21</v>
       </c>
       <c r="W149" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="X149" t="s" s="2">
         <v>21</v>
@@ -21212,19 +21233,19 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>21</v>
@@ -21247,14 +21268,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -21270,7 +21291,7 @@
         <v>21</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>219</v>
@@ -21294,17 +21315,17 @@
         <v>21</v>
       </c>
       <c r="T150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W150" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="U150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="X150" t="s" s="2">
         <v>21</v>
       </c>
@@ -21330,7 +21351,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>704</v>
+        <v>595</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -21342,13 +21363,13 @@
         <v>21</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>21</v>
@@ -21357,7 +21378,7 @@
         <v>21</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>707</v>
+        <v>21</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>21</v>
@@ -21365,21 +21386,21 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>21</v>
@@ -21394,14 +21415,12 @@
         <v>219</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>21</v>
@@ -21414,7 +21433,7 @@
         <v>21</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>21</v>
@@ -21450,7 +21469,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21465,10 +21484,10 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>21</v>
+        <v>710</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>21</v>
@@ -21477,7 +21496,7 @@
         <v>21</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>21</v>
@@ -21485,21 +21504,21 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>21</v>
@@ -21514,12 +21533,14 @@
         <v>219</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>716</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -21532,7 +21553,7 @@
         <v>21</v>
       </c>
       <c r="T152" t="s" s="2">
-        <v>21</v>
+        <v>718</v>
       </c>
       <c r="U152" t="s" s="2">
         <v>21</v>
@@ -21568,7 +21589,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21583,10 +21604,10 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>722</v>
+        <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>21</v>
@@ -21595,7 +21616,7 @@
         <v>21</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>21</v>
@@ -21603,14 +21624,14 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -21632,10 +21653,10 @@
         <v>219</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21650,7 +21671,7 @@
         <v>21</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>729</v>
+        <v>21</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>21</v>
@@ -21686,7 +21707,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21701,10 +21722,10 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>21</v>
@@ -21713,7 +21734,7 @@
         <v>21</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="AP153" t="s" s="2">
         <v>21</v>
@@ -21721,14 +21742,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -21750,14 +21771,12 @@
         <v>219</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -21770,7 +21789,7 @@
         <v>21</v>
       </c>
       <c r="T154" t="s" s="2">
-        <v>21</v>
+        <v>734</v>
       </c>
       <c r="U154" t="s" s="2">
         <v>21</v>
@@ -21806,7 +21825,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21821,10 +21840,10 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>21</v>
@@ -21833,7 +21852,7 @@
         <v>21</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="AP154" t="s" s="2">
         <v>21</v>
@@ -21841,10 +21860,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21855,7 +21874,7 @@
         <v>81</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>21</v>
@@ -21867,18 +21886,18 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" t="s" s="2">
-        <v>745</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>21</v>
       </c>
@@ -21890,7 +21909,7 @@
         <v>21</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>746</v>
+        <v>21</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>21</v>
@@ -21926,7 +21945,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21941,10 +21960,10 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>21</v>
+        <v>744</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>522</v>
+        <v>745</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>21</v>
@@ -21953,7 +21972,7 @@
         <v>21</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="AP155" t="s" s="2">
         <v>21</v>
@@ -21961,10 +21980,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21975,7 +21994,7 @@
         <v>81</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>21</v>
@@ -21984,20 +22003,20 @@
         <v>21</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>21</v>
@@ -22010,7 +22029,7 @@
         <v>21</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>21</v>
+        <v>751</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>21</v>
@@ -22022,13 +22041,13 @@
         <v>21</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>753</v>
+        <v>21</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>754</v>
+        <v>21</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>21</v>
@@ -22046,7 +22065,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -22064,16 +22083,16 @@
         <v>21</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>755</v>
+        <v>522</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>756</v>
+        <v>21</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>21</v>
@@ -22081,10 +22100,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22107,16 +22126,18 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>149</v>
+        <v>755</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>150</v>
+        <v>756</v>
       </c>
       <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+      <c r="O157" t="s" s="2">
+        <v>757</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>21</v>
       </c>
@@ -22140,13 +22161,13 @@
         <v>21</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>21</v>
+        <v>758</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>21</v>
+        <v>759</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>21</v>
@@ -22164,7 +22185,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>151</v>
+        <v>754</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -22176,22 +22197,22 @@
         <v>21</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>153</v>
+        <v>760</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>21</v>
+        <v>761</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>21</v>
+        <v>762</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>21</v>
@@ -22199,21 +22220,21 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>21</v>
@@ -22225,17 +22246,15 @@
         <v>21</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -22272,31 +22291,31 @@
         <v>21</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>21</v>
@@ -22319,14 +22338,14 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22342,23 +22361,21 @@
         <v>21</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>21</v>
       </c>
@@ -22394,19 +22411,19 @@
         <v>21</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>288</v>
+        <v>161</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22418,13 +22435,13 @@
         <v>21</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>289</v>
+        <v>153</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>21</v>
@@ -22433,7 +22450,7 @@
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>21</v>
@@ -22441,10 +22458,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22455,7 +22472,7 @@
         <v>81</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>21</v>
@@ -22464,19 +22481,23 @@
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>149</v>
+        <v>284</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>21</v>
       </c>
@@ -22524,25 +22545,25 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>153</v>
+        <v>289</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>21</v>
@@ -22551,7 +22572,7 @@
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AP160" t="s" s="2">
         <v>21</v>
@@ -22559,21 +22580,21 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>21</v>
@@ -22585,17 +22606,15 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -22632,31 +22651,31 @@
         <v>21</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>21</v>
@@ -22679,21 +22698,21 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>21</v>
@@ -22702,23 +22721,21 @@
         <v>21</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>297</v>
+        <v>157</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>21</v>
       </c>
@@ -22754,37 +22771,37 @@
         <v>21</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>302</v>
+        <v>161</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>764</v>
+        <v>21</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>303</v>
+        <v>153</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>21</v>
@@ -22793,7 +22810,7 @@
         <v>21</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>21</v>
@@ -22801,10 +22818,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22827,18 +22844,20 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
       </c>
@@ -22886,7 +22905,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22901,10 +22920,10 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>21</v>
+        <v>769</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>21</v>
@@ -22913,7 +22932,7 @@
         <v>21</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>21</v>
@@ -22921,10 +22940,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22947,18 +22966,18 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>21</v>
       </c>
@@ -23006,7 +23025,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23021,10 +23040,10 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>767</v>
+        <v>21</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>21</v>
@@ -23033,7 +23052,7 @@
         <v>21</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>21</v>
@@ -23041,10 +23060,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23067,17 +23086,17 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -23126,7 +23145,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23141,10 +23160,10 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>21</v>
@@ -23153,7 +23172,7 @@
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>21</v>
@@ -23161,10 +23180,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23187,19 +23206,17 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -23248,7 +23265,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23263,10 +23280,10 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>21</v>
+        <v>774</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>21</v>
@@ -23275,7 +23292,7 @@
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>21</v>
@@ -23283,10 +23300,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23309,19 +23326,19 @@
         <v>91</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -23370,7 +23387,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23388,7 +23405,7 @@
         <v>21</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>21</v>
@@ -23397,7 +23414,7 @@
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>21</v>
@@ -23405,10 +23422,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23428,22 +23445,22 @@
         <v>21</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>773</v>
+        <v>219</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>774</v>
+        <v>342</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>775</v>
+        <v>343</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>776</v>
+        <v>344</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>777</v>
+        <v>345</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
@@ -23480,17 +23497,19 @@
         <v>21</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AC168" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>614</v>
+        <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>772</v>
+        <v>346</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23508,16 +23527,16 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>778</v>
+        <v>347</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>779</v>
+        <v>348</v>
       </c>
       <c r="AP168" t="s" s="2">
         <v>21</v>
@@ -23525,14 +23544,12 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>781</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>21</v>
       </c>
@@ -23553,19 +23570,19 @@
         <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>332</v>
+        <v>778</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
@@ -23602,19 +23619,17 @@
         <v>21</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="AC169" s="2"/>
       <c r="AD169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>21</v>
+        <v>614</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23629,10 +23644,10 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>153</v>
@@ -23641,7 +23656,7 @@
         <v>21</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>21</v>
@@ -23649,13 +23664,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>21</v>
@@ -23677,19 +23692,19 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>784</v>
+        <v>332</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
@@ -23738,7 +23753,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23756,7 +23771,7 @@
         <v>153</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>153</v>
@@ -23765,7 +23780,7 @@
         <v>21</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="AP170" t="s" s="2">
         <v>21</v>
@@ -23773,12 +23788,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="C171" s="2"/>
+        <v>777</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>788</v>
+      </c>
       <c r="D171" t="s" s="2">
         <v>21</v>
       </c>
@@ -23787,7 +23804,7 @@
         <v>81</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>21</v>
@@ -23799,19 +23816,19 @@
         <v>21</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -23860,13 +23877,13 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>21</v>
@@ -23878,7 +23895,7 @@
         <v>153</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>153</v>
@@ -23887,7 +23904,7 @@
         <v>21</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>21</v>
@@ -23895,10 +23912,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23921,19 +23938,19 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>794</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -23982,7 +23999,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23994,13 +24011,13 @@
         <v>21</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>799</v>
+        <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>153</v>
@@ -24009,7 +24026,7 @@
         <v>21</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>21</v>
+        <v>797</v>
       </c>
       <c r="AP172" t="s" s="2">
         <v>21</v>
@@ -24017,10 +24034,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24031,7 +24048,7 @@
         <v>81</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>21</v>
@@ -24043,16 +24060,20 @@
         <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>219</v>
+        <v>799</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
       </c>
@@ -24100,28 +24121,28 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>151</v>
+        <v>798</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>21</v>
+        <v>804</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="AM173" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>21</v>
@@ -24135,21 +24156,21 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>21</v>
@@ -24161,17 +24182,15 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>21</v>
@@ -24220,19 +24239,19 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>21</v>
@@ -24255,14 +24274,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>804</v>
+        <v>156</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -24275,26 +24294,24 @@
         <v>21</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>805</v>
+        <v>157</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>806</v>
+        <v>221</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O175" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>21</v>
       </c>
@@ -24342,7 +24359,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>807</v>
+        <v>161</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24360,7 +24377,7 @@
         <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>21</v>
@@ -24384,7 +24401,7 @@
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>21</v>
+        <v>809</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -24397,23 +24414,25 @@
         <v>21</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="N176" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O176" t="s" s="2">
-        <v>811</v>
+        <v>206</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>21</v>
@@ -24438,31 +24457,31 @@
         <v>21</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF176" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -24474,22 +24493,22 @@
         <v>21</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>814</v>
+        <v>21</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>21</v>
@@ -24497,10 +24516,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24511,7 +24530,7 @@
         <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>21</v>
@@ -24523,16 +24542,18 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>149</v>
+        <v>814</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>150</v>
+        <v>815</v>
       </c>
       <c r="N177" s="2"/>
-      <c r="O177" s="2"/>
+      <c r="O177" t="s" s="2">
+        <v>816</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
       </c>
@@ -24556,13 +24577,13 @@
         <v>21</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>21</v>
+        <v>817</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>21</v>
+        <v>818</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -24580,34 +24601,34 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>151</v>
+        <v>813</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM177" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM177" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>21</v>
+        <v>819</v>
       </c>
       <c r="AP177" t="s" s="2">
         <v>21</v>
@@ -24615,21 +24636,21 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>21</v>
@@ -24641,17 +24662,15 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -24688,31 +24707,31 @@
         <v>21</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>21</v>
@@ -24735,14 +24754,14 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -24758,23 +24777,21 @@
         <v>21</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>21</v>
       </c>
@@ -24810,19 +24827,19 @@
         <v>21</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>288</v>
+        <v>161</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24834,13 +24851,13 @@
         <v>21</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>289</v>
+        <v>153</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>21</v>
@@ -24849,7 +24866,7 @@
         <v>21</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AP179" t="s" s="2">
         <v>21</v>
@@ -24857,10 +24874,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24871,7 +24888,7 @@
         <v>81</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>21</v>
@@ -24880,19 +24897,23 @@
         <v>21</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>149</v>
+        <v>284</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>21</v>
       </c>
@@ -24940,25 +24961,25 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>153</v>
+        <v>289</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>21</v>
@@ -24967,7 +24988,7 @@
         <v>21</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>21</v>
@@ -24975,21 +24996,21 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>21</v>
@@ -25001,17 +25022,15 @@
         <v>21</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -25048,31 +25067,31 @@
         <v>21</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>21</v>
@@ -25095,21 +25114,21 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>21</v>
@@ -25118,23 +25137,21 @@
         <v>21</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>297</v>
+        <v>157</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>21</v>
       </c>
@@ -25170,37 +25187,37 @@
         <v>21</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>302</v>
+        <v>161</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>821</v>
+        <v>21</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>303</v>
+        <v>153</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>21</v>
@@ -25209,7 +25226,7 @@
         <v>21</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AP182" t="s" s="2">
         <v>21</v>
@@ -25217,10 +25234,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25243,18 +25260,20 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>21</v>
       </c>
@@ -25302,7 +25321,7 @@
         <v>21</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25317,10 +25336,10 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>21</v>
+        <v>826</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>21</v>
@@ -25329,7 +25348,7 @@
         <v>21</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AP183" t="s" s="2">
         <v>21</v>
@@ -25337,10 +25356,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25363,18 +25382,18 @@
         <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>21</v>
       </c>
@@ -25422,7 +25441,7 @@
         <v>21</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25437,10 +25456,10 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>824</v>
+        <v>21</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>21</v>
@@ -25449,7 +25468,7 @@
         <v>21</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>21</v>
@@ -25457,10 +25476,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25483,17 +25502,17 @@
         <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>21</v>
@@ -25542,7 +25561,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25557,10 +25576,10 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>21</v>
@@ -25569,7 +25588,7 @@
         <v>21</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>21</v>
@@ -25577,10 +25596,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25603,19 +25622,17 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>21</v>
@@ -25664,7 +25681,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25679,10 +25696,10 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>21</v>
+        <v>831</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>21</v>
@@ -25691,7 +25708,7 @@
         <v>21</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="AP186" t="s" s="2">
         <v>21</v>
@@ -25699,10 +25716,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25725,19 +25742,19 @@
         <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>21</v>
@@ -25786,7 +25803,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25804,7 +25821,7 @@
         <v>21</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>21</v>
@@ -25813,7 +25830,7 @@
         <v>21</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>21</v>
@@ -25821,10 +25838,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25844,20 +25861,22 @@
         <v>21</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>457</v>
+        <v>219</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>830</v>
+        <v>342</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O188" t="s" s="2">
-        <v>832</v>
+        <v>345</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -25906,7 +25925,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>829</v>
+        <v>346</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25924,16 +25943,16 @@
         <v>21</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>463</v>
+        <v>347</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>833</v>
+        <v>348</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>21</v>
@@ -25967,16 +25986,18 @@
         <v>21</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>219</v>
+        <v>457</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>149</v>
+        <v>835</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>150</v>
+        <v>836</v>
       </c>
       <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+      <c r="O189" t="s" s="2">
+        <v>837</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>21</v>
       </c>
@@ -26024,7 +26045,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>151</v>
+        <v>834</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26036,22 +26057,22 @@
         <v>21</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL189" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM189" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM189" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN189" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>21</v>
+        <v>838</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>21</v>
@@ -26059,21 +26080,21 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>21</v>
@@ -26085,17 +26106,15 @@
         <v>21</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>21</v>
@@ -26132,31 +26151,31 @@
         <v>21</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>21</v>
@@ -26179,46 +26198,44 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I191" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>468</v>
+        <v>157</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>469</v>
+        <v>221</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>21</v>
       </c>
@@ -26242,49 +26259,49 @@
         <v>21</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>473</v>
+        <v>21</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC191" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>474</v>
+        <v>161</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>475</v>
+        <v>153</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>21</v>
@@ -26293,7 +26310,7 @@
         <v>21</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>21</v>
@@ -26301,10 +26318,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26321,25 +26338,25 @@
         <v>21</v>
       </c>
       <c r="I192" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J192" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>21</v>
@@ -26364,13 +26381,13 @@
         <v>21</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>21</v>
@@ -26388,7 +26405,7 @@
         <v>21</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -26406,7 +26423,7 @@
         <v>21</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>21</v>
@@ -26415,7 +26432,7 @@
         <v>21</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>21</v>
@@ -26423,14 +26440,14 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>486</v>
+        <v>21</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -26452,15 +26469,17 @@
         <v>219</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>21</v>
       </c>
@@ -26508,7 +26527,7 @@
         <v>21</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -26523,10 +26542,10 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>839</v>
+        <v>21</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>21</v>
@@ -26535,7 +26554,7 @@
         <v>21</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>21</v>
@@ -26543,21 +26562,21 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>21</v>
@@ -26572,13 +26591,13 @@
         <v>219</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26628,13 +26647,13 @@
         <v>21</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>21</v>
@@ -26643,10 +26662,10 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>21</v>
@@ -26655,7 +26674,7 @@
         <v>21</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>21</v>
@@ -26663,14 +26682,14 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -26692,12 +26711,14 @@
         <v>219</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N195" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>21</v>
@@ -26746,7 +26767,7 @@
         <v>21</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26761,10 +26782,10 @@
         <v>102</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>21</v>
+        <v>846</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>21</v>
@@ -26773,7 +26794,7 @@
         <v>21</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>21</v>
@@ -26781,10 +26802,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26810,10 +26831,10 @@
         <v>219</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26864,7 +26885,7 @@
         <v>21</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -26882,7 +26903,7 @@
         <v>21</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>21</v>
@@ -26891,7 +26912,7 @@
         <v>21</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>21</v>
@@ -26899,10 +26920,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26913,7 +26934,7 @@
         <v>81</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>21</v>
@@ -26925,18 +26946,16 @@
         <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N197" s="2"/>
-      <c r="O197" t="s" s="2">
-        <v>520</v>
-      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>21</v>
       </c>
@@ -26984,13 +27003,13 @@
         <v>21</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>21</v>
@@ -27002,7 +27021,7 @@
         <v>21</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>21</v>
@@ -27011,7 +27030,7 @@
         <v>21</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>21</v>
@@ -27019,10 +27038,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27033,7 +27052,7 @@
         <v>81</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>21</v>
@@ -27042,22 +27061,20 @@
         <v>21</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>525</v>
+        <v>191</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>846</v>
+        <v>518</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>848</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>21</v>
@@ -27106,13 +27123,13 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>845</v>
+        <v>521</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>21</v>
@@ -27124,16 +27141,16 @@
         <v>21</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN198" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>849</v>
+        <v>523</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>21</v>
@@ -27155,7 +27172,7 @@
         <v>81</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>21</v>
@@ -27167,16 +27184,20 @@
         <v>21</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>219</v>
+        <v>525</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>149</v>
+        <v>851</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
+        <v>852</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P199" t="s" s="2">
         <v>21</v>
       </c>
@@ -27224,34 +27245,34 @@
         <v>21</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>151</v>
+        <v>850</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL199" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM199" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM199" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN199" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>21</v>
+        <v>854</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>21</v>
@@ -27259,21 +27280,21 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>21</v>
@@ -27285,17 +27306,15 @@
         <v>21</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>21</v>
@@ -27332,31 +27351,31 @@
         <v>21</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI200" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>21</v>
@@ -27379,21 +27398,21 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>21</v>
@@ -27402,18 +27421,20 @@
         <v>21</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>536</v>
+        <v>157</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N201" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>21</v>
@@ -27438,49 +27459,49 @@
         <v>21</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>538</v>
+        <v>21</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>539</v>
+        <v>21</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC201" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>540</v>
+        <v>161</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>853</v>
+        <v>21</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>543</v>
+        <v>153</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>21</v>
@@ -27489,7 +27510,7 @@
         <v>21</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>544</v>
+        <v>21</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>21</v>
@@ -27497,10 +27518,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27523,20 +27544,16 @@
         <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N202" s="2"/>
+      <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
         <v>21</v>
       </c>
@@ -27560,13 +27577,13 @@
         <v>21</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>21</v>
+        <v>538</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>21</v>
+        <v>539</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>21</v>
@@ -27584,7 +27601,7 @@
         <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27593,16 +27610,16 @@
         <v>90</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>21</v>
+        <v>541</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>21</v>
@@ -27611,7 +27628,7 @@
         <v>21</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AP202" t="s" s="2">
         <v>21</v>
@@ -27619,10 +27636,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27639,25 +27656,25 @@
         <v>21</v>
       </c>
       <c r="I203" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J203" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>21</v>
@@ -27682,13 +27699,13 @@
         <v>21</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>559</v>
+        <v>21</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>21</v>
@@ -27706,7 +27723,7 @@
         <v>21</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27721,10 +27738,10 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>475</v>
+        <v>551</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>21</v>
@@ -27733,7 +27750,7 @@
         <v>21</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="AP203" t="s" s="2">
         <v>21</v>
@@ -27741,10 +27758,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27761,24 +27778,26 @@
         <v>21</v>
       </c>
       <c r="I204" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J204" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>564</v>
+        <v>110</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O204" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="O204" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P204" t="s" s="2">
         <v>21</v>
       </c>
@@ -27802,13 +27821,13 @@
         <v>21</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>21</v>
+        <v>558</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>21</v>
+        <v>559</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>21</v>
@@ -27826,7 +27845,7 @@
         <v>21</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -27841,10 +27860,10 @@
         <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>21</v>
+        <v>862</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>153</v>
+        <v>475</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>21</v>
@@ -27853,7 +27872,7 @@
         <v>21</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>153</v>
+        <v>562</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>21</v>
@@ -27861,10 +27880,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27887,15 +27906,17 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>191</v>
+        <v>564</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N205" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>21</v>
@@ -27944,7 +27965,7 @@
         <v>21</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -27962,7 +27983,7 @@
         <v>21</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>522</v>
+        <v>153</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>21</v>
@@ -27971,7 +27992,7 @@
         <v>21</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>21</v>
@@ -27979,10 +28000,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28002,23 +28023,19 @@
         <v>21</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>625</v>
+        <v>191</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>626</v>
+        <v>570</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>861</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N206" s="2"/>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>21</v>
       </c>
@@ -28066,7 +28083,7 @@
         <v>21</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>860</v>
+        <v>572</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -28075,16 +28092,16 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>630</v>
+        <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>631</v>
+        <v>522</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>21</v>
@@ -28093,7 +28110,7 @@
         <v>21</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>632</v>
+        <v>133</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>21</v>
@@ -28101,10 +28118,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28127,16 +28144,20 @@
         <v>21</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>219</v>
+        <v>625</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>149</v>
+        <v>626</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
+        <v>627</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>866</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>21</v>
       </c>
@@ -28184,7 +28205,7 @@
         <v>21</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>151</v>
+        <v>865</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28193,16 +28214,16 @@
         <v>90</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>21</v>
+        <v>630</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>153</v>
+        <v>631</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>21</v>
@@ -28211,7 +28232,7 @@
         <v>21</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>21</v>
+        <v>632</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>21</v>
@@ -28219,21 +28240,21 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>21</v>
@@ -28245,17 +28266,15 @@
         <v>21</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>21</v>
@@ -28292,31 +28311,31 @@
         <v>21</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC208" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AD208" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>21</v>
@@ -28339,46 +28358,44 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>636</v>
+        <v>157</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>637</v>
+        <v>221</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>21</v>
       </c>
@@ -28390,7 +28407,7 @@
         <v>21</v>
       </c>
       <c r="T209" t="s" s="2">
-        <v>640</v>
+        <v>21</v>
       </c>
       <c r="U209" t="s" s="2">
         <v>21</v>
@@ -28402,49 +28419,49 @@
         <v>21</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>641</v>
+        <v>21</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>642</v>
+        <v>21</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>643</v>
+        <v>161</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>865</v>
+        <v>21</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>475</v>
+        <v>153</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>21</v>
@@ -28453,7 +28470,7 @@
         <v>21</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>645</v>
+        <v>21</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>21</v>
@@ -28461,12 +28478,14 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="C210" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="D210" t="s" s="2">
         <v>21</v>
       </c>
@@ -28484,20 +28503,18 @@
         <v>21</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>110</v>
+        <v>637</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>21</v>
@@ -28510,7 +28527,7 @@
         <v>21</v>
       </c>
       <c r="T210" t="s" s="2">
-        <v>650</v>
+        <v>21</v>
       </c>
       <c r="U210" t="s" s="2">
         <v>21</v>
@@ -28522,13 +28539,13 @@
         <v>21</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>651</v>
+        <v>21</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>652</v>
+        <v>21</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>21</v>
@@ -28546,25 +28563,25 @@
         <v>21</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>653</v>
+        <v>161</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>21</v>
@@ -28573,7 +28590,7 @@
         <v>21</v>
       </c>
       <c r="AO210" t="s" s="2">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="AP210" t="s" s="2">
         <v>21</v>
@@ -28581,10 +28598,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28601,25 +28618,25 @@
         <v>21</v>
       </c>
       <c r="I211" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J211" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>481</v>
+        <v>644</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>21</v>
@@ -28632,7 +28649,7 @@
         <v>21</v>
       </c>
       <c r="T211" t="s" s="2">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="U211" t="s" s="2">
         <v>21</v>
@@ -28644,13 +28661,13 @@
         <v>21</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>21</v>
+        <v>646</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>21</v>
+        <v>647</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>21</v>
@@ -28668,7 +28685,7 @@
         <v>21</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28683,10 +28700,10 @@
         <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>21</v>
@@ -28695,7 +28712,7 @@
         <v>21</v>
       </c>
       <c r="AO211" t="s" s="2">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="AP211" t="s" s="2">
         <v>21</v>
@@ -28703,10 +28720,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28717,7 +28734,7 @@
         <v>81</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>21</v>
@@ -28729,15 +28746,17 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>21</v>
@@ -28750,7 +28769,7 @@
         <v>21</v>
       </c>
       <c r="T212" t="s" s="2">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="U212" t="s" s="2">
         <v>21</v>
@@ -28762,13 +28781,13 @@
         <v>21</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>21</v>
+        <v>656</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>21</v>
@@ -28786,13 +28805,13 @@
         <v>21</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>21</v>
@@ -28801,10 +28820,10 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>870</v>
+        <v>21</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>669</v>
+        <v>475</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>21</v>
@@ -28813,7 +28832,7 @@
         <v>21</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>21</v>
@@ -28821,10 +28840,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28844,19 +28863,23 @@
         <v>21</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>219</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>585</v>
+        <v>661</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>21</v>
       </c>
@@ -28868,7 +28891,7 @@
         <v>21</v>
       </c>
       <c r="T213" t="s" s="2">
-        <v>21</v>
+        <v>664</v>
       </c>
       <c r="U213" t="s" s="2">
         <v>21</v>
@@ -28904,7 +28927,7 @@
         <v>21</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>151</v>
+        <v>665</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -28916,13 +28939,13 @@
         <v>21</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>21</v>
+        <v>874</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>21</v>
@@ -28931,7 +28954,7 @@
         <v>21</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>21</v>
+        <v>667</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>21</v>
@@ -28939,10 +28962,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28962,16 +28985,16 @@
         <v>21</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>136</v>
+        <v>669</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>137</v>
+        <v>670</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -28986,7 +29009,7 @@
         <v>21</v>
       </c>
       <c r="T214" t="s" s="2">
-        <v>21</v>
+        <v>671</v>
       </c>
       <c r="U214" t="s" s="2">
         <v>21</v>
@@ -29010,17 +29033,19 @@
         <v>21</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC214" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC214" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD214" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>161</v>
+        <v>672</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -29032,13 +29057,13 @@
         <v>21</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>21</v>
+        <v>876</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>21</v>
+        <v>674</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>21</v>
@@ -29047,7 +29072,7 @@
         <v>21</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>21</v>
+        <v>675</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>21</v>
@@ -29055,14 +29080,12 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>21</v>
       </c>
@@ -29083,13 +29106,13 @@
         <v>21</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>675</v>
+        <v>219</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>676</v>
+        <v>585</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>677</v>
+        <v>586</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -29140,25 +29163,25 @@
         <v>21</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>678</v>
+        <v>21</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>21</v>
@@ -29175,14 +29198,12 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>680</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
         <v>21</v>
       </c>
@@ -29191,7 +29212,7 @@
         <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>21</v>
@@ -29203,13 +29224,13 @@
         <v>21</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>681</v>
+        <v>135</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>682</v>
+        <v>136</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>683</v>
+        <v>137</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -29248,16 +29269,14 @@
         <v>21</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC216" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC216" s="2"/>
       <c r="AD216" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF216" t="s" s="2">
         <v>161</v>
@@ -29278,7 +29297,7 @@
         <v>21</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>684</v>
+        <v>21</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>21</v>
@@ -29295,13 +29314,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>21</v>
@@ -29323,13 +29342,13 @@
         <v>21</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -29398,7 +29417,7 @@
         <v>21</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>21</v>
@@ -29415,13 +29434,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>21</v>
@@ -29443,13 +29462,13 @@
         <v>21</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -29509,7 +29528,7 @@
         <v>82</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>141</v>
@@ -29518,7 +29537,7 @@
         <v>21</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>21</v>
+        <v>689</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>21</v>
@@ -29535,12 +29554,14 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="C219" s="2"/>
+        <v>878</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="D219" t="s" s="2">
         <v>21</v>
       </c>
@@ -29561,13 +29582,13 @@
         <v>21</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>219</v>
+        <v>692</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -29591,7 +29612,7 @@
         <v>21</v>
       </c>
       <c r="W219" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="X219" t="s" s="2">
         <v>21</v>
@@ -29618,25 +29639,25 @@
         <v>21</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>21</v>
+        <v>694</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>21</v>
@@ -29653,14 +29674,16 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>878</v>
       </c>
-      <c r="C220" s="2"/>
+      <c r="C220" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="D220" t="s" s="2">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
@@ -29676,16 +29699,16 @@
         <v>21</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>219</v>
+        <v>697</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -29700,7 +29723,7 @@
         <v>21</v>
       </c>
       <c r="T220" t="s" s="2">
-        <v>703</v>
+        <v>21</v>
       </c>
       <c r="U220" t="s" s="2">
         <v>21</v>
@@ -29736,25 +29759,25 @@
         <v>21</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>704</v>
+        <v>161</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>879</v>
+        <v>21</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>21</v>
@@ -29763,7 +29786,7 @@
         <v>21</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>707</v>
+        <v>21</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>21</v>
@@ -29771,21 +29794,21 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>709</v>
+        <v>21</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>21</v>
@@ -29794,20 +29817,18 @@
         <v>21</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K221" t="s" s="2">
         <v>219</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="N221" s="2"/>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>21</v>
@@ -29820,7 +29841,7 @@
         <v>21</v>
       </c>
       <c r="T221" t="s" s="2">
-        <v>713</v>
+        <v>21</v>
       </c>
       <c r="U221" t="s" s="2">
         <v>21</v>
@@ -29829,7 +29850,7 @@
         <v>21</v>
       </c>
       <c r="W221" t="s" s="2">
-        <v>21</v>
+        <v>703</v>
       </c>
       <c r="X221" t="s" s="2">
         <v>21</v>
@@ -29856,7 +29877,7 @@
         <v>21</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>714</v>
+        <v>595</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -29868,13 +29889,13 @@
         <v>21</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>715</v>
+        <v>21</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>21</v>
@@ -29883,7 +29904,7 @@
         <v>21</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>716</v>
+        <v>21</v>
       </c>
       <c r="AP221" t="s" s="2">
         <v>21</v>
@@ -29891,14 +29912,14 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
@@ -29920,10 +29941,10 @@
         <v>219</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -29938,7 +29959,7 @@
         <v>21</v>
       </c>
       <c r="T222" t="s" s="2">
-        <v>21</v>
+        <v>708</v>
       </c>
       <c r="U222" t="s" s="2">
         <v>21</v>
@@ -29974,7 +29995,7 @@
         <v>21</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -29989,10 +30010,10 @@
         <v>102</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="AM222" t="s" s="2">
         <v>21</v>
@@ -30001,7 +30022,7 @@
         <v>21</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>21</v>
@@ -30009,21 +30030,21 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>21</v>
@@ -30038,12 +30059,14 @@
         <v>219</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N223" s="2"/>
+        <v>716</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>21</v>
@@ -30056,7 +30079,7 @@
         <v>21</v>
       </c>
       <c r="T223" t="s" s="2">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="U223" t="s" s="2">
         <v>21</v>
@@ -30092,7 +30115,7 @@
         <v>21</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30107,10 +30130,10 @@
         <v>102</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>884</v>
+        <v>21</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="AM223" t="s" s="2">
         <v>21</v>
@@ -30119,7 +30142,7 @@
         <v>21</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>21</v>
@@ -30127,14 +30150,14 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>21</v>
+        <v>723</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -30156,14 +30179,12 @@
         <v>219</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>21</v>
@@ -30212,7 +30233,7 @@
         <v>21</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -30227,10 +30248,10 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>21</v>
@@ -30239,7 +30260,7 @@
         <v>21</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>21</v>
@@ -30247,21 +30268,21 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>21</v>
@@ -30273,18 +30294,16 @@
         <v>91</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="N225" s="2"/>
-      <c r="O225" t="s" s="2">
-        <v>745</v>
-      </c>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>21</v>
       </c>
@@ -30296,7 +30315,7 @@
         <v>21</v>
       </c>
       <c r="T225" t="s" s="2">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="U225" t="s" s="2">
         <v>21</v>
@@ -30332,7 +30351,7 @@
         <v>21</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30347,10 +30366,10 @@
         <v>102</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>21</v>
+        <v>890</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>522</v>
+        <v>737</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>21</v>
@@ -30359,7 +30378,7 @@
         <v>21</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>21</v>
@@ -30367,10 +30386,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30390,21 +30409,21 @@
         <v>21</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>574</v>
+        <v>740</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="N226" s="2"/>
-      <c r="O226" t="s" s="2">
-        <v>890</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>21</v>
       </c>
@@ -30428,13 +30447,13 @@
         <v>21</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>578</v>
+        <v>21</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>579</v>
+        <v>21</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>21</v>
@@ -30452,7 +30471,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>888</v>
+        <v>743</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -30467,19 +30486,19 @@
         <v>102</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>153</v>
+        <v>892</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>581</v>
+        <v>745</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN226" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>891</v>
+        <v>746</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>21</v>
@@ -30487,10 +30506,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30501,7 +30520,7 @@
         <v>81</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>21</v>
@@ -30510,19 +30529,21 @@
         <v>21</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>585</v>
+        <v>748</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>586</v>
+        <v>749</v>
       </c>
       <c r="N227" s="2"/>
-      <c r="O227" s="2"/>
+      <c r="O227" t="s" s="2">
+        <v>750</v>
+      </c>
       <c r="P227" t="s" s="2">
         <v>21</v>
       </c>
@@ -30534,7 +30555,7 @@
         <v>21</v>
       </c>
       <c r="T227" t="s" s="2">
-        <v>21</v>
+        <v>751</v>
       </c>
       <c r="U227" t="s" s="2">
         <v>21</v>
@@ -30570,7 +30591,7 @@
         <v>21</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>151</v>
+        <v>752</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -30582,13 +30603,13 @@
         <v>21</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>21</v>
@@ -30597,7 +30618,7 @@
         <v>21</v>
       </c>
       <c r="AO227" t="s" s="2">
-        <v>21</v>
+        <v>753</v>
       </c>
       <c r="AP227" t="s" s="2">
         <v>21</v>
@@ -30605,10 +30626,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30619,7 +30640,7 @@
         <v>81</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>21</v>
@@ -30631,16 +30652,18 @@
         <v>21</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>136</v>
+        <v>574</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>137</v>
+        <v>895</v>
       </c>
       <c r="N228" s="2"/>
-      <c r="O228" s="2"/>
+      <c r="O228" t="s" s="2">
+        <v>896</v>
+      </c>
       <c r="P228" t="s" s="2">
         <v>21</v>
       </c>
@@ -30664,56 +30687,58 @@
         <v>21</v>
       </c>
       <c r="X228" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>21</v>
+        <v>578</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB228" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC228" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE228" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>161</v>
+        <v>894</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>21</v>
+        <v>581</v>
       </c>
       <c r="AM228" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AN228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>21</v>
+        <v>897</v>
       </c>
       <c r="AP228" t="s" s="2">
         <v>21</v>
@@ -30721,14 +30746,12 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>898</v>
+      </c>
+      <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>21</v>
       </c>
@@ -30749,13 +30772,13 @@
         <v>21</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>590</v>
+        <v>219</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30806,19 +30829,19 @@
         <v>21</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>21</v>
@@ -30841,10 +30864,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30855,7 +30878,7 @@
         <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>21</v>
@@ -30867,13 +30890,13 @@
         <v>21</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>594</v>
+        <v>136</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>594</v>
+        <v>137</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -30912,31 +30935,29 @@
         <v>21</v>
       </c>
       <c r="AB230" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC230" s="2"/>
       <c r="AD230" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE230" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>21</v>
@@ -30959,12 +30980,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="C231" s="2"/>
+        <v>899</v>
+      </c>
+      <c r="C231" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="D231" t="s" s="2">
         <v>21</v>
       </c>
@@ -30985,18 +31008,16 @@
         <v>21</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>264</v>
+        <v>590</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>897</v>
+        <v>591</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>898</v>
+        <v>592</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>899</v>
-      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>21</v>
       </c>
@@ -31044,34 +31065,34 @@
         <v>21</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>896</v>
+        <v>161</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>900</v>
+        <v>152</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>901</v>
+        <v>21</v>
       </c>
       <c r="AL231" t="s" s="2">
-        <v>902</v>
+        <v>21</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>903</v>
+        <v>21</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>21</v>
@@ -31079,10 +31100,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31105,13 +31126,13 @@
         <v>21</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>905</v>
+        <v>594</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>906</v>
+        <v>594</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -31162,7 +31183,7 @@
         <v>21</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>904</v>
+        <v>595</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31174,16 +31195,16 @@
         <v>21</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AL232" t="s" s="2">
-        <v>907</v>
+        <v>21</v>
       </c>
       <c r="AM232" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN232" t="s" s="2">
         <v>21</v>
@@ -31197,10 +31218,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31211,7 +31232,7 @@
         <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>21</v>
@@ -31223,19 +31244,17 @@
         <v>21</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>794</v>
+        <v>264</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>911</v>
-      </c>
+        <v>904</v>
+      </c>
+      <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>21</v>
@@ -31284,34 +31303,34 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>21</v>
+        <v>906</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>21</v>
+        <v>907</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AM233" t="s" s="2">
-        <v>914</v>
+        <v>153</v>
       </c>
       <c r="AN233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>21</v>
+        <v>909</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>21</v>
@@ -31319,10 +31338,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31345,13 +31364,13 @@
         <v>21</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>149</v>
+        <v>911</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>150</v>
+        <v>912</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31402,7 +31421,7 @@
         <v>21</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>151</v>
+        <v>910</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -31414,16 +31433,16 @@
         <v>21</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AL234" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="AM234" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AM234" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN234" t="s" s="2">
         <v>21</v>
@@ -31437,14 +31456,14 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
@@ -31463,18 +31482,20 @@
         <v>21</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>135</v>
+        <v>799</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>157</v>
+        <v>915</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>221</v>
+        <v>916</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O235" s="2"/>
+        <v>917</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>918</v>
+      </c>
       <c r="P235" t="s" s="2">
         <v>21</v>
       </c>
@@ -31522,7 +31543,7 @@
         <v>21</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>161</v>
+        <v>914</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31534,16 +31555,16 @@
         <v>21</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>153</v>
+        <v>919</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>21</v>
+        <v>920</v>
       </c>
       <c r="AN235" t="s" s="2">
         <v>21</v>
@@ -31557,46 +31578,42 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>804</v>
+        <v>21</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I236" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>805</v>
+        <v>149</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>21</v>
       </c>
@@ -31644,25 +31661,25 @@
         <v>21</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>807</v>
+        <v>151</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>21</v>
@@ -31679,21 +31696,21 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>21</v>
@@ -31705,20 +31722,18 @@
         <v>21</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>919</v>
+        <v>157</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>920</v>
+        <v>221</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>922</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
         <v>21</v>
       </c>
@@ -31742,13 +31757,13 @@
         <v>21</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>21</v>
@@ -31766,34 +31781,34 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>918</v>
+        <v>161</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>923</v>
+        <v>21</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>924</v>
+        <v>153</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>925</v>
+        <v>21</v>
       </c>
       <c r="AN237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>926</v>
+        <v>21</v>
       </c>
       <c r="AP237" t="s" s="2">
         <v>21</v>
@@ -31801,45 +31816,45 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>21</v>
+        <v>809</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I238" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J238" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>332</v>
+        <v>135</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>928</v>
+        <v>810</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>929</v>
+        <v>811</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>930</v>
+        <v>159</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>931</v>
+        <v>206</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>21</v>
@@ -31888,34 +31903,34 @@
         <v>21</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>927</v>
+        <v>812</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>932</v>
+        <v>21</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>933</v>
+        <v>133</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>934</v>
+        <v>21</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>935</v>
+        <v>21</v>
       </c>
       <c r="AP238" t="s" s="2">
         <v>21</v>
@@ -31923,21 +31938,21 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>937</v>
+        <v>21</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>21</v>
@@ -31949,18 +31964,20 @@
         <v>21</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>938</v>
+        <v>176</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="O239" s="2"/>
+        <v>927</v>
+      </c>
+      <c r="O239" t="s" s="2">
+        <v>928</v>
+      </c>
       <c r="P239" t="s" s="2">
         <v>21</v>
       </c>
@@ -31984,13 +32001,13 @@
         <v>21</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y239" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="Z239" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>21</v>
@@ -32008,13 +32025,13 @@
         <v>21</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI239" t="s" s="2">
         <v>21</v>
@@ -32023,19 +32040,19 @@
         <v>102</v>
       </c>
       <c r="AK239" t="s" s="2">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>153</v>
+        <v>931</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="AP239" t="s" s="2">
         <v>21</v>
@@ -32043,10 +32060,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32066,22 +32083,22 @@
         <v>21</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>21</v>
@@ -32130,7 +32147,7 @@
         <v>21</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -32145,19 +32162,19 @@
         <v>102</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>902</v>
+        <v>939</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO240" t="s" s="2">
-        <v>21</v>
+        <v>941</v>
       </c>
       <c r="AP240" t="s" s="2">
         <v>21</v>
@@ -32165,14 +32182,14 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>21</v>
+        <v>943</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -32185,26 +32202,24 @@
         <v>21</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>794</v>
+        <v>944</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>956</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>21</v>
       </c>
@@ -32252,7 +32267,7 @@
         <v>21</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -32267,10 +32282,10 @@
         <v>102</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>21</v>
+        <v>948</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="AM241" t="s" s="2">
         <v>153</v>
@@ -32279,7 +32294,7 @@
         <v>21</v>
       </c>
       <c r="AO241" t="s" s="2">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AP241" t="s" s="2">
         <v>21</v>
@@ -32287,10 +32302,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32310,19 +32325,23 @@
         <v>21</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>149</v>
+        <v>952</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
+        <v>953</v>
+      </c>
+      <c r="N242" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="O242" t="s" s="2">
+        <v>955</v>
+      </c>
       <c r="P242" t="s" s="2">
         <v>21</v>
       </c>
@@ -32370,7 +32389,7 @@
         <v>21</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>151</v>
+        <v>951</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -32382,16 +32401,16 @@
         <v>21</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK242" t="s" s="2">
-        <v>21</v>
+        <v>956</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>153</v>
+        <v>908</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>21</v>
+        <v>957</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>21</v>
@@ -32405,14 +32424,14 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
@@ -32425,24 +32444,26 @@
         <v>21</v>
       </c>
       <c r="I243" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J243" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>135</v>
+        <v>799</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>157</v>
+        <v>959</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>221</v>
+        <v>960</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O243" s="2"/>
+        <v>961</v>
+      </c>
+      <c r="O243" t="s" s="2">
+        <v>962</v>
+      </c>
       <c r="P243" t="s" s="2">
         <v>21</v>
       </c>
@@ -32490,7 +32511,7 @@
         <v>21</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>161</v>
+        <v>958</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -32502,16 +32523,16 @@
         <v>21</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL243" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="AM243" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>21</v>
@@ -32525,46 +32546,42 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
-        <v>804</v>
+        <v>21</v>
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I244" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J244" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>805</v>
+        <v>149</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
         <v>21</v>
       </c>
@@ -32612,25 +32629,25 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>807</v>
+        <v>151</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="AM244" t="s" s="2">
         <v>21</v>
@@ -32647,21 +32664,21 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>21</v>
@@ -32670,19 +32687,19 @@
         <v>21</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>962</v>
+        <v>135</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>963</v>
+        <v>157</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>964</v>
+        <v>221</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>965</v>
+        <v>159</v>
       </c>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
@@ -32732,34 +32749,34 @@
         <v>21</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>961</v>
+        <v>161</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK245" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL245" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL245" t="s" s="2">
-        <v>214</v>
-      </c>
       <c r="AM245" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>966</v>
+        <v>21</v>
       </c>
       <c r="AP245" t="s" s="2">
         <v>21</v>
@@ -32767,42 +32784,46 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
-        <v>21</v>
+        <v>809</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I246" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J246" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O246" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P246" t="s" s="2">
         <v>21</v>
       </c>
@@ -32826,60 +32847,298 @@
         <v>21</v>
       </c>
       <c r="X246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF246" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="AG246" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH246" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ246" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL246" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP246" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="L247" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="M247" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="O247" s="2"/>
+      <c r="P247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL247" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM247" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO247" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="AP247" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="N248" s="2"/>
+      <c r="O248" s="2"/>
+      <c r="P248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q248" s="2"/>
+      <c r="R248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X248" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="Y246" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>967</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
+      <c r="Y248" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK246" t="s" s="2">
+      <c r="AK248" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL246" t="s" s="2">
-        <v>971</v>
-      </c>
-      <c r="AM246" t="s" s="2">
+      <c r="AL248" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="AM248" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP246" t="s" s="2">
+      <c r="AN248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP248" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:53:56+00:00</t>
+    <t>2024-10-31T15:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:15:50+00:00</t>
+    <t>2024-11-17T20:36:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:36:22+00:00</t>
+    <t>2024-11-17T21:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:23:25+00:00</t>
+    <t>2024-11-27T13:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:38:13+00:00</t>
+    <t>2024-12-15T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T13:48:39+00:00</t>
+    <t>2024-12-19T09:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9649" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9647" uniqueCount="991">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T09:41:53+00:00</t>
+    <t>2025-01-08T15:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -682,25 +682,6 @@
   <si>
     <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
 </t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>XAD</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1996,7 +1977,25 @@
     <t>Patient.address</t>
   </si>
   <si>
+    <t>An address for the individual</t>
+  </si>
+  <si>
+    <t>An address for the individual.</t>
+  </si>
+  <si>
+    <t>Patient may have multiple addresses with different uses or applicable periods.</t>
+  </si>
+  <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
+  </si>
+  <si>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>.addr</t>
+  </si>
+  <si>
+    <t>PID-11</t>
   </si>
   <si>
     <t>Patient.address.id</t>
@@ -2720,7 +2719,16 @@
     <t>Patient.contact.address</t>
   </si>
   <si>
+    <t>Address for the contact person</t>
+  </si>
+  <si>
+    <t>Address for the contact person.</t>
+  </si>
+  <si>
     <t>Need to keep track where the contact person can be contacted per postal mail or visited.</t>
+  </si>
+  <si>
+    <t>NK1-4</t>
   </si>
   <si>
     <t>Patient.contact.address.id</t>
@@ -6906,14 +6914,12 @@
         <v>213</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -6971,16 +6977,16 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -6989,7 +6995,7 @@
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>21</v>
@@ -6997,10 +7003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -7026,16 +7032,16 @@
         <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>159</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -7084,7 +7090,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -7119,10 +7125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -7145,17 +7151,17 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -7192,7 +7198,7 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
@@ -7202,7 +7208,7 @@
         <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -7220,16 +7226,16 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>21</v>
@@ -7237,10 +7243,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7263,7 +7269,7 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>149</v>
@@ -7355,10 +7361,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7387,7 +7393,7 @@
         <v>157</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>159</v>
@@ -7475,10 +7481,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7504,16 +7510,16 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -7538,13 +7544,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -7562,7 +7568,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7580,7 +7586,7 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -7597,10 +7603,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7626,16 +7632,16 @@
         <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -7664,7 +7670,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -7682,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7700,7 +7706,7 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -7709,7 +7715,7 @@
         <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>21</v>
@@ -7717,10 +7723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7746,16 +7752,16 @@
         <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -7768,7 +7774,7 @@
         <v>21</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>21</v>
@@ -7804,7 +7810,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7822,7 +7828,7 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -7831,7 +7837,7 @@
         <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>21</v>
@@ -7839,10 +7845,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7865,16 +7871,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7888,7 +7894,7 @@
         <v>21</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>21</v>
@@ -7924,7 +7930,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7942,7 +7948,7 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -7951,7 +7957,7 @@
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>21</v>
@@ -7959,10 +7965,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7988,10 +7994,10 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8042,7 +8048,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -8060,7 +8066,7 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -8069,7 +8075,7 @@
         <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>21</v>
@@ -8077,10 +8083,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8103,16 +8109,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -8162,7 +8168,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -8180,7 +8186,7 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -8189,7 +8195,7 @@
         <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>21</v>
@@ -8197,13 +8203,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>21</v>
@@ -8225,17 +8231,17 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -8284,7 +8290,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -8302,16 +8308,16 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>21</v>
@@ -8319,10 +8325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8345,7 +8351,7 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>149</v>
@@ -8437,10 +8443,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8469,7 +8475,7 @@
         <v>157</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>159</v>
@@ -8557,10 +8563,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8586,16 +8592,16 @@
         <v>110</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -8620,13 +8626,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -8644,7 +8650,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8662,7 +8668,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -8679,10 +8685,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8708,16 +8714,16 @@
         <v>176</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -8742,11 +8748,11 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -8764,7 +8770,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8782,7 +8788,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -8791,7 +8797,7 @@
         <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>21</v>
@@ -8799,10 +8805,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8825,7 +8831,7 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>149</v>
@@ -8917,10 +8923,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8949,7 +8955,7 @@
         <v>157</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>159</v>
@@ -9037,10 +9043,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9063,19 +9069,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -9124,7 +9130,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -9142,7 +9148,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -9151,7 +9157,7 @@
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>21</v>
@@ -9159,10 +9165,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9185,7 +9191,7 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>149</v>
@@ -9277,10 +9283,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9309,7 +9315,7 @@
         <v>157</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>159</v>
@@ -9397,10 +9403,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9426,23 +9432,23 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>21</v>
@@ -9484,7 +9490,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9502,7 +9508,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -9511,7 +9517,7 @@
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>21</v>
@@ -9519,10 +9525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9545,16 +9551,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9604,7 +9610,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9622,7 +9628,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -9631,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
@@ -9639,10 +9645,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9668,21 +9674,21 @@
         <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>21</v>
@@ -9724,7 +9730,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9742,7 +9748,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -9751,7 +9757,7 @@
         <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>21</v>
@@ -9759,10 +9765,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9785,17 +9791,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -9844,7 +9850,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9862,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -9871,7 +9877,7 @@
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>21</v>
@@ -9879,10 +9885,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9905,19 +9911,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -9966,7 +9972,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9984,7 +9990,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -9993,7 +9999,7 @@
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>21</v>
@@ -10001,10 +10007,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10027,19 +10033,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -10088,7 +10094,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -10106,7 +10112,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -10115,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>21</v>
@@ -10123,10 +10129,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10152,29 +10158,29 @@
         <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>21</v>
@@ -10210,7 +10216,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10225,10 +10231,10 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -10237,7 +10243,7 @@
         <v>21</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>21</v>
@@ -10245,10 +10251,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10271,16 +10277,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10294,7 +10300,7 @@
         <v>21</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>21</v>
@@ -10330,7 +10336,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10345,10 +10351,10 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -10357,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>21</v>
@@ -10365,10 +10371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10394,10 +10400,10 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10448,7 +10454,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10466,7 +10472,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -10475,7 +10481,7 @@
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>21</v>
@@ -10483,10 +10489,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10509,16 +10515,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10568,7 +10574,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10586,7 +10592,7 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -10595,7 +10601,7 @@
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>21</v>
@@ -10603,10 +10609,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10629,7 +10635,7 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>149</v>
@@ -10721,10 +10727,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10753,7 +10759,7 @@
         <v>157</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>159</v>
@@ -10841,10 +10847,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10867,16 +10873,16 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10926,7 +10932,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10935,7 +10941,7 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
@@ -10961,10 +10967,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10990,13 +10996,13 @@
         <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -11025,10 +11031,10 @@
         <v>179</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -11046,7 +11052,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -11081,10 +11087,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11107,16 +11113,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -11166,7 +11172,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11184,7 +11190,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
@@ -11201,10 +11207,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11227,16 +11233,16 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11244,7 +11250,7 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>21</v>
@@ -11286,7 +11292,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11321,13 +11327,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
@@ -11349,17 +11355,17 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -11408,7 +11414,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11426,16 +11432,16 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>21</v>
@@ -11443,10 +11449,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11469,7 +11475,7 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>149</v>
@@ -11561,10 +11567,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11593,7 +11599,7 @@
         <v>157</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>159</v>
@@ -11681,10 +11687,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11710,16 +11716,16 @@
         <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -11744,13 +11750,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -11768,7 +11774,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11786,7 +11792,7 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
@@ -11803,10 +11809,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11832,16 +11838,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -11866,11 +11872,11 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -11888,7 +11894,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11906,7 +11912,7 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
@@ -11915,7 +11921,7 @@
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>21</v>
@@ -11923,10 +11929,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11949,7 +11955,7 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>149</v>
@@ -12041,10 +12047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12073,7 +12079,7 @@
         <v>157</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>159</v>
@@ -12161,10 +12167,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12187,19 +12193,19 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -12248,7 +12254,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12266,7 +12272,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -12275,7 +12281,7 @@
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>21</v>
@@ -12283,10 +12289,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12309,7 +12315,7 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>149</v>
@@ -12401,10 +12407,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12433,7 +12439,7 @@
         <v>157</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
@@ -12521,10 +12527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12550,23 +12556,23 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>21</v>
@@ -12608,7 +12614,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12626,7 +12632,7 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -12635,7 +12641,7 @@
         <v>21</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>21</v>
@@ -12643,10 +12649,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12669,16 +12675,16 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12728,7 +12734,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12746,7 +12752,7 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
@@ -12755,7 +12761,7 @@
         <v>21</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>21</v>
@@ -12763,10 +12769,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12792,21 +12798,21 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>21</v>
@@ -12848,7 +12854,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12866,7 +12872,7 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
@@ -12875,7 +12881,7 @@
         <v>21</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>21</v>
@@ -12883,10 +12889,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12909,17 +12915,17 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -12968,7 +12974,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12986,7 +12992,7 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -12995,7 +13001,7 @@
         <v>21</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>21</v>
@@ -13003,10 +13009,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13029,19 +13035,19 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -13090,7 +13096,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -13108,7 +13114,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
@@ -13117,7 +13123,7 @@
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>21</v>
@@ -13125,10 +13131,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13151,19 +13157,19 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -13212,7 +13218,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13230,7 +13236,7 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
@@ -13239,7 +13245,7 @@
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>21</v>
@@ -13247,10 +13253,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13276,29 +13282,29 @@
         <v>104</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>21</v>
@@ -13334,7 +13340,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13349,10 +13355,10 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -13361,7 +13367,7 @@
         <v>21</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>21</v>
@@ -13369,10 +13375,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13395,16 +13401,16 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13418,7 +13424,7 @@
         <v>21</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>21</v>
@@ -13454,7 +13460,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13469,10 +13475,10 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -13481,7 +13487,7 @@
         <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>21</v>
@@ -13489,10 +13495,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13518,10 +13524,10 @@
         <v>191</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13572,7 +13578,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13590,7 +13596,7 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -13599,7 +13605,7 @@
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>21</v>
@@ -13607,10 +13613,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13633,16 +13639,16 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13692,7 +13698,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13710,7 +13716,7 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -13719,7 +13725,7 @@
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>21</v>
@@ -13727,10 +13733,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13753,7 +13759,7 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>149</v>
@@ -13845,10 +13851,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13877,7 +13883,7 @@
         <v>157</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>159</v>
@@ -13965,10 +13971,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13991,16 +13997,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14050,7 +14056,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -14059,7 +14065,7 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -14085,10 +14091,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14114,13 +14120,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -14149,10 +14155,10 @@
         <v>179</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -14170,7 +14176,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -14205,10 +14211,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14231,16 +14237,16 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14290,7 +14296,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14308,7 +14314,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>
@@ -14325,10 +14331,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14351,16 +14357,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14368,7 +14374,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>21</v>
@@ -14410,7 +14416,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14445,13 +14451,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>21</v>
@@ -14473,17 +14479,17 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -14532,7 +14538,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14550,16 +14556,16 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>21</v>
@@ -14567,10 +14573,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14593,7 +14599,7 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>149</v>
@@ -14685,10 +14691,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14717,7 +14723,7 @@
         <v>157</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>159</v>
@@ -14805,10 +14811,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14834,16 +14840,16 @@
         <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -14868,13 +14874,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -14892,7 +14898,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14910,7 +14916,7 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -14927,10 +14933,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14956,16 +14962,16 @@
         <v>176</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -14990,11 +14996,11 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -15012,7 +15018,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -15030,7 +15036,7 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
@@ -15039,7 +15045,7 @@
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>21</v>
@@ -15047,10 +15053,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15073,7 +15079,7 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>149</v>
@@ -15165,10 +15171,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15197,7 +15203,7 @@
         <v>157</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>159</v>
@@ -15285,10 +15291,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15311,19 +15317,19 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -15372,7 +15378,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15390,7 +15396,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>21</v>
@@ -15399,7 +15405,7 @@
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>21</v>
@@ -15407,10 +15413,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15433,7 +15439,7 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>149</v>
@@ -15525,10 +15531,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15557,7 +15563,7 @@
         <v>157</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>159</v>
@@ -15645,10 +15651,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15674,23 +15680,23 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>21</v>
@@ -15732,7 +15738,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15750,7 +15756,7 @@
         <v>21</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>21</v>
@@ -15759,7 +15765,7 @@
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>21</v>
@@ -15767,10 +15773,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15793,16 +15799,16 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15852,7 +15858,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15870,7 +15876,7 @@
         <v>21</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>21</v>
@@ -15879,7 +15885,7 @@
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>21</v>
@@ -15887,10 +15893,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15916,21 +15922,21 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>21</v>
@@ -15972,7 +15978,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15990,7 +15996,7 @@
         <v>21</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
@@ -15999,7 +16005,7 @@
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>21</v>
@@ -16007,10 +16013,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16033,17 +16039,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -16092,7 +16098,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16110,7 +16116,7 @@
         <v>21</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>21</v>
@@ -16119,7 +16125,7 @@
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>21</v>
@@ -16127,10 +16133,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16153,19 +16159,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -16214,7 +16220,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16232,7 +16238,7 @@
         <v>21</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -16241,7 +16247,7 @@
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>21</v>
@@ -16249,10 +16255,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16275,19 +16281,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -16336,7 +16342,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16354,7 +16360,7 @@
         <v>21</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>21</v>
@@ -16363,7 +16369,7 @@
         <v>21</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>21</v>
@@ -16371,10 +16377,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16400,16 +16406,16 @@
         <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -16422,7 +16428,7 @@
         <v>21</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>21</v>
@@ -16458,7 +16464,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16473,10 +16479,10 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -16485,7 +16491,7 @@
         <v>21</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>21</v>
@@ -16493,10 +16499,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16519,16 +16525,16 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16542,7 +16548,7 @@
         <v>21</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>21</v>
@@ -16578,7 +16584,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16593,10 +16599,10 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
@@ -16605,7 +16611,7 @@
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>21</v>
@@ -16613,10 +16619,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16642,10 +16648,10 @@
         <v>191</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16696,7 +16702,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16714,7 +16720,7 @@
         <v>21</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>21</v>
@@ -16723,7 +16729,7 @@
         <v>21</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>21</v>
@@ -16731,10 +16737,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16757,16 +16763,16 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16816,7 +16822,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16834,7 +16840,7 @@
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>21</v>
@@ -16843,7 +16849,7 @@
         <v>21</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>21</v>
@@ -16851,10 +16857,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16877,25 +16883,25 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>21</v>
@@ -16940,7 +16946,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16958,13 +16964,13 @@
         <v>153</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>153</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -16975,10 +16981,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17001,19 +17007,19 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -17062,7 +17068,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -17077,19 +17083,19 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>21</v>
@@ -17097,10 +17103,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17123,7 +17129,7 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>149</v>
@@ -17215,10 +17221,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17247,7 +17253,7 @@
         <v>157</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>159</v>
@@ -17335,10 +17341,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17364,16 +17370,16 @@
         <v>110</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -17398,13 +17404,13 @@
         <v>21</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>21</v>
@@ -17422,7 +17428,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17440,7 +17446,7 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>21</v>
@@ -17449,7 +17455,7 @@
         <v>21</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>21</v>
@@ -17457,10 +17463,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17483,19 +17489,19 @@
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -17544,7 +17550,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17562,7 +17568,7 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>21</v>
@@ -17571,7 +17577,7 @@
         <v>21</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>21</v>
@@ -17579,14 +17585,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17605,16 +17611,16 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17664,7 +17670,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17679,10 +17685,10 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -17691,7 +17697,7 @@
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>21</v>
@@ -17699,14 +17705,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17725,16 +17731,16 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17784,7 +17790,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17799,10 +17805,10 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>21</v>
@@ -17811,7 +17817,7 @@
         <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>21</v>
@@ -17819,10 +17825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17845,13 +17851,13 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17902,7 +17908,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17917,10 +17923,10 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>21</v>
@@ -17929,7 +17935,7 @@
         <v>21</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>21</v>
@@ -17937,10 +17943,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17963,13 +17969,13 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18020,7 +18026,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18035,10 +18041,10 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>21</v>
@@ -18047,7 +18053,7 @@
         <v>21</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>21</v>
@@ -18055,10 +18061,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18084,14 +18090,14 @@
         <v>191</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -18140,7 +18146,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -18158,7 +18164,7 @@
         <v>21</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>21</v>
@@ -18167,7 +18173,7 @@
         <v>21</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>21</v>
@@ -18175,10 +18181,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18201,19 +18207,19 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -18262,7 +18268,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18280,16 +18286,16 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>21</v>
@@ -18297,10 +18303,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18323,7 +18329,7 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>149</v>
@@ -18415,10 +18421,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18447,7 +18453,7 @@
         <v>157</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>159</v>
@@ -18535,10 +18541,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18564,10 +18570,10 @@
         <v>110</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18594,13 +18600,13 @@
         <v>21</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -18618,7 +18624,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18627,16 +18633,16 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
@@ -18645,7 +18651,7 @@
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>21</v>
@@ -18653,10 +18659,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18679,19 +18685,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -18740,7 +18746,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18755,10 +18761,10 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>21</v>
@@ -18767,7 +18773,7 @@
         <v>21</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>21</v>
@@ -18775,10 +18781,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18804,16 +18810,16 @@
         <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -18838,13 +18844,13 @@
         <v>21</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>21</v>
@@ -18862,7 +18868,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18877,10 +18883,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
@@ -18889,7 +18895,7 @@
         <v>21</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AP129" t="s" s="2">
         <v>21</v>
@@ -18897,10 +18903,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18923,16 +18929,16 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18982,7 +18988,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -19017,10 +19023,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19046,10 +19052,10 @@
         <v>191</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -19100,7 +19106,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -19118,7 +19124,7 @@
         <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>21</v>
@@ -19135,10 +19141,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19164,16 +19170,16 @@
         <v>110</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>21</v>
@@ -19198,13 +19204,13 @@
         <v>21</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
@@ -19222,7 +19228,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19237,19 +19243,19 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>21</v>
@@ -19257,10 +19263,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19283,13 +19289,13 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19375,10 +19381,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19491,13 +19497,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>21</v>
@@ -19519,13 +19525,13 @@
         <v>21</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19611,10 +19617,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19637,13 +19643,13 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19694,7 +19700,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19729,10 +19735,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19755,19 +19761,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>21</v>
@@ -19816,7 +19822,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19831,30 +19837,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19877,19 +19883,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>21</v>
@@ -19926,17 +19932,17 @@
         <v>21</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="AC138" s="2"/>
       <c r="AD138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19954,7 +19960,7 @@
         <v>21</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>153</v>
@@ -19963,7 +19969,7 @@
         <v>21</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>21</v>
@@ -19971,13 +19977,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
@@ -19999,19 +20005,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -20060,7 +20066,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -20075,10 +20081,10 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>153</v>
@@ -20087,7 +20093,7 @@
         <v>21</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>21</v>
@@ -20095,13 +20101,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>21</v>
@@ -20123,19 +20129,19 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>21</v>
@@ -20184,7 +20190,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20199,10 +20205,10 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>153</v>
@@ -20211,7 +20217,7 @@
         <v>21</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>21</v>
@@ -20219,10 +20225,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20242,22 +20248,22 @@
         <v>21</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>213</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>214</v>
+        <v>636</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>215</v>
+        <v>637</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>216</v>
+        <v>638</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>21</v>
@@ -20306,7 +20312,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -20315,25 +20321,25 @@
         <v>82</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>218</v>
+        <v>640</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>21</v>
+        <v>641</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>219</v>
+        <v>642</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>21</v>
@@ -20367,7 +20373,7 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>149</v>
@@ -20491,7 +20497,7 @@
         <v>157</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>159</v>
@@ -20762,7 +20768,7 @@
         <v>21</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y145" t="s" s="2">
         <v>656</v>
@@ -20804,7 +20810,7 @@
         <v>659</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>21</v>
@@ -20882,7 +20888,7 @@
         <v>21</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y146" t="s" s="2">
         <v>666</v>
@@ -20924,7 +20930,7 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>21</v>
@@ -20967,7 +20973,7 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>671</v>
@@ -20979,7 +20985,7 @@
         <v>673</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>21</v>
@@ -21046,7 +21052,7 @@
         <v>676</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>21</v>
@@ -21089,7 +21095,7 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L148" t="s" s="2">
         <v>679</v>
@@ -21207,13 +21213,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21921,7 +21927,7 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L155" t="s" s="2">
         <v>711</v>
@@ -21978,7 +21984,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22039,7 +22045,7 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>716</v>
@@ -22157,7 +22163,7 @@
         <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L157" t="s" s="2">
         <v>725</v>
@@ -22277,7 +22283,7 @@
         <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L158" t="s" s="2">
         <v>734</v>
@@ -22395,7 +22401,7 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>742</v>
@@ -22513,7 +22519,7 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>750</v>
@@ -22710,7 +22716,7 @@
         <v>21</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>21</v>
@@ -22873,7 +22879,7 @@
         <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>149</v>
@@ -22997,7 +23003,7 @@
         <v>157</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>159</v>
@@ -23111,19 +23117,19 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -23172,7 +23178,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23190,7 +23196,7 @@
         <v>21</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>21</v>
@@ -23199,7 +23205,7 @@
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>21</v>
@@ -23233,7 +23239,7 @@
         <v>21</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>149</v>
@@ -23357,7 +23363,7 @@
         <v>157</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>159</v>
@@ -23474,16 +23480,16 @@
         <v>104</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
@@ -23532,7 +23538,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23550,7 +23556,7 @@
         <v>779</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>21</v>
@@ -23559,7 +23565,7 @@
         <v>21</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AP168" t="s" s="2">
         <v>21</v>
@@ -23593,16 +23599,16 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23652,7 +23658,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23670,7 +23676,7 @@
         <v>21</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>21</v>
@@ -23679,7 +23685,7 @@
         <v>21</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>21</v>
@@ -23716,14 +23722,14 @@
         <v>110</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
@@ -23772,7 +23778,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23790,7 +23796,7 @@
         <v>782</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>21</v>
@@ -23799,7 +23805,7 @@
         <v>21</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AP170" t="s" s="2">
         <v>21</v>
@@ -23833,17 +23839,17 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -23892,7 +23898,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23910,7 +23916,7 @@
         <v>784</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>21</v>
@@ -23919,7 +23925,7 @@
         <v>21</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>21</v>
@@ -23953,19 +23959,19 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -24014,7 +24020,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -24032,7 +24038,7 @@
         <v>21</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>21</v>
@@ -24041,7 +24047,7 @@
         <v>21</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP172" t="s" s="2">
         <v>21</v>
@@ -24075,19 +24081,19 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -24136,7 +24142,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24154,7 +24160,7 @@
         <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>21</v>
@@ -24163,7 +24169,7 @@
         <v>21</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>21</v>
@@ -24246,14 +24252,14 @@
         <v>21</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="AC174" s="2"/>
       <c r="AD174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="AF174" t="s" s="2">
         <v>787</v>
@@ -24319,7 +24325,7 @@
         <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L175" t="s" s="2">
         <v>789</v>
@@ -24809,7 +24815,7 @@
         <v>21</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>149</v>
@@ -24933,7 +24939,7 @@
         <v>157</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>159</v>
@@ -25059,7 +25065,7 @@
         <v>159</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -25289,7 +25295,7 @@
         <v>21</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L183" t="s" s="2">
         <v>149</v>
@@ -25413,7 +25419,7 @@
         <v>157</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N184" t="s" s="2">
         <v>159</v>
@@ -25527,19 +25533,19 @@
         <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>21</v>
@@ -25588,7 +25594,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25606,7 +25612,7 @@
         <v>21</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>21</v>
@@ -25615,7 +25621,7 @@
         <v>21</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>21</v>
@@ -25649,7 +25655,7 @@
         <v>21</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>149</v>
@@ -25773,7 +25779,7 @@
         <v>157</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N187" t="s" s="2">
         <v>159</v>
@@ -25890,16 +25896,16 @@
         <v>104</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -25948,7 +25954,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25966,7 +25972,7 @@
         <v>836</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>21</v>
@@ -25975,7 +25981,7 @@
         <v>21</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>21</v>
@@ -26009,16 +26015,16 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -26068,7 +26074,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26086,7 +26092,7 @@
         <v>21</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>21</v>
@@ -26095,7 +26101,7 @@
         <v>21</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>21</v>
@@ -26132,14 +26138,14 @@
         <v>110</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>21</v>
@@ -26188,7 +26194,7 @@
         <v>21</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -26206,7 +26212,7 @@
         <v>839</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>21</v>
@@ -26215,7 +26221,7 @@
         <v>21</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>21</v>
@@ -26249,17 +26255,17 @@
         <v>91</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>21</v>
@@ -26308,7 +26314,7 @@
         <v>21</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -26326,7 +26332,7 @@
         <v>841</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>21</v>
@@ -26335,7 +26341,7 @@
         <v>21</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>21</v>
@@ -26369,19 +26375,19 @@
         <v>91</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>21</v>
@@ -26430,7 +26436,7 @@
         <v>21</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -26448,7 +26454,7 @@
         <v>21</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>21</v>
@@ -26457,7 +26463,7 @@
         <v>21</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>21</v>
@@ -26491,19 +26497,19 @@
         <v>91</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>21</v>
@@ -26552,7 +26558,7 @@
         <v>21</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -26570,7 +26576,7 @@
         <v>21</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>21</v>
@@ -26579,7 +26585,7 @@
         <v>21</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>21</v>
@@ -26613,7 +26619,7 @@
         <v>21</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L194" t="s" s="2">
         <v>845</v>
@@ -26690,7 +26696,7 @@
         <v>21</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>153</v>
@@ -26733,7 +26739,7 @@
         <v>21</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L195" t="s" s="2">
         <v>149</v>
@@ -26857,7 +26863,7 @@
         <v>157</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>159</v>
@@ -26974,16 +26980,16 @@
         <v>110</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>21</v>
@@ -27008,13 +27014,13 @@
         <v>21</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>21</v>
@@ -27032,7 +27038,7 @@
         <v>21</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -27050,7 +27056,7 @@
         <v>21</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>21</v>
@@ -27059,7 +27065,7 @@
         <v>21</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>21</v>
@@ -27093,19 +27099,19 @@
         <v>91</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>21</v>
@@ -27154,7 +27160,7 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -27172,7 +27178,7 @@
         <v>21</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>21</v>
@@ -27181,7 +27187,7 @@
         <v>21</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>21</v>
@@ -27196,7 +27202,7 @@
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -27215,16 +27221,16 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -27274,7 +27280,7 @@
         <v>21</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -27292,7 +27298,7 @@
         <v>854</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>21</v>
@@ -27301,7 +27307,7 @@
         <v>21</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>21</v>
@@ -27316,7 +27322,7 @@
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -27335,16 +27341,16 @@
         <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -27394,7 +27400,7 @@
         <v>21</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -27412,7 +27418,7 @@
         <v>856</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>21</v>
@@ -27421,7 +27427,7 @@
         <v>21</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>21</v>
@@ -27455,13 +27461,13 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -27512,7 +27518,7 @@
         <v>21</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -27530,7 +27536,7 @@
         <v>21</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>21</v>
@@ -27539,7 +27545,7 @@
         <v>21</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>21</v>
@@ -27573,13 +27579,13 @@
         <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -27630,7 +27636,7 @@
         <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27648,7 +27654,7 @@
         <v>21</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>21</v>
@@ -27657,7 +27663,7 @@
         <v>21</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="AP202" t="s" s="2">
         <v>21</v>
@@ -27694,14 +27700,14 @@
         <v>191</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>21</v>
@@ -27750,7 +27756,7 @@
         <v>21</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27768,7 +27774,7 @@
         <v>21</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>21</v>
@@ -27777,7 +27783,7 @@
         <v>21</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AP203" t="s" s="2">
         <v>21</v>
@@ -27811,7 +27817,7 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>861</v>
@@ -27823,7 +27829,7 @@
         <v>863</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>21</v>
@@ -27890,7 +27896,7 @@
         <v>21</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>153</v>
@@ -27933,7 +27939,7 @@
         <v>21</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L205" t="s" s="2">
         <v>149</v>
@@ -28057,7 +28063,7 @@
         <v>157</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N206" t="s" s="2">
         <v>159</v>
@@ -28174,10 +28180,10 @@
         <v>110</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -28204,13 +28210,13 @@
         <v>21</v>
       </c>
       <c r="X207" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y207" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="Z207" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>21</v>
@@ -28228,7 +28234,7 @@
         <v>21</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28237,7 +28243,7 @@
         <v>90</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="AJ207" t="s" s="2">
         <v>102</v>
@@ -28246,7 +28252,7 @@
         <v>868</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>21</v>
@@ -28255,7 +28261,7 @@
         <v>21</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>21</v>
@@ -28289,19 +28295,19 @@
         <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>21</v>
@@ -28350,7 +28356,7 @@
         <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28368,7 +28374,7 @@
         <v>870</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>21</v>
@@ -28377,7 +28383,7 @@
         <v>21</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>21</v>
@@ -28414,16 +28420,16 @@
         <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>21</v>
@@ -28448,13 +28454,13 @@
         <v>21</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>21</v>
@@ -28472,7 +28478,7 @@
         <v>21</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28490,7 +28496,7 @@
         <v>872</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>21</v>
@@ -28499,7 +28505,7 @@
         <v>21</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>21</v>
@@ -28533,16 +28539,16 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28592,7 +28598,7 @@
         <v>21</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -28656,10 +28662,10 @@
         <v>191</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -28710,7 +28716,7 @@
         <v>21</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28728,7 +28734,7 @@
         <v>21</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>21</v>
@@ -28774,16 +28780,14 @@
         <v>213</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>214</v>
+        <v>876</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="N212" s="2"/>
       <c r="O212" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>21</v>
@@ -28841,25 +28845,25 @@
         <v>90</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>218</v>
+        <v>640</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>219</v>
+        <v>879</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>21</v>
@@ -28867,10 +28871,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28893,7 +28897,7 @@
         <v>21</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>149</v>
@@ -28985,10 +28989,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29017,7 +29021,7 @@
         <v>157</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>159</v>
@@ -29105,10 +29109,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C215" t="s" s="2">
         <v>646</v>
@@ -29225,10 +29229,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29288,7 +29292,7 @@
         <v>21</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y216" t="s" s="2">
         <v>656</v>
@@ -29327,10 +29331,10 @@
         <v>102</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>21</v>
@@ -29347,10 +29351,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29408,7 +29412,7 @@
         <v>21</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y217" t="s" s="2">
         <v>666</v>
@@ -29450,7 +29454,7 @@
         <v>21</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>21</v>
@@ -29467,10 +29471,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29493,7 +29497,7 @@
         <v>91</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>671</v>
@@ -29505,7 +29509,7 @@
         <v>673</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>21</v>
@@ -29569,10 +29573,10 @@
         <v>102</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>21</v>
@@ -29589,10 +29593,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29615,7 +29619,7 @@
         <v>91</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L219" t="s" s="2">
         <v>679</v>
@@ -29687,7 +29691,7 @@
         <v>102</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>684</v>
@@ -29707,10 +29711,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29733,13 +29737,13 @@
         <v>21</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -29825,10 +29829,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29941,10 +29945,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C222" t="s" s="2">
         <v>689</v>
@@ -30061,10 +30065,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>695</v>
@@ -30181,10 +30185,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="B224" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="B224" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="C224" t="s" s="2">
         <v>701</v>
@@ -30301,10 +30305,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C225" t="s" s="2">
         <v>706</v>
@@ -30421,10 +30425,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30447,7 +30451,7 @@
         <v>21</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L226" t="s" s="2">
         <v>711</v>
@@ -30504,7 +30508,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -30539,10 +30543,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30565,7 +30569,7 @@
         <v>91</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L227" t="s" s="2">
         <v>716</v>
@@ -30637,7 +30641,7 @@
         <v>102</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="AL227" t="s" s="2">
         <v>721</v>
@@ -30657,10 +30661,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30683,7 +30687,7 @@
         <v>91</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L228" t="s" s="2">
         <v>725</v>
@@ -30777,10 +30781,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30803,7 +30807,7 @@
         <v>91</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L229" t="s" s="2">
         <v>734</v>
@@ -30875,7 +30879,7 @@
         <v>102</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="AL229" t="s" s="2">
         <v>738</v>
@@ -30895,10 +30899,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30921,7 +30925,7 @@
         <v>91</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L230" t="s" s="2">
         <v>742</v>
@@ -30993,7 +30997,7 @@
         <v>102</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="AL230" t="s" s="2">
         <v>747</v>
@@ -31013,10 +31017,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31039,7 +31043,7 @@
         <v>91</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L231" t="s" s="2">
         <v>750</v>
@@ -31113,7 +31117,7 @@
         <v>102</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="AL231" t="s" s="2">
         <v>755</v>
@@ -31133,10 +31137,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31236,7 +31240,7 @@
         <v>21</v>
       </c>
       <c r="AL232" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM232" t="s" s="2">
         <v>21</v>
@@ -31253,10 +31257,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31282,14 +31286,14 @@
         <v>110</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>21</v>
@@ -31314,13 +31318,13 @@
         <v>21</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>21</v>
@@ -31338,7 +31342,7 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31356,7 +31360,7 @@
         <v>153</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="AM233" t="s" s="2">
         <v>153</v>
@@ -31365,7 +31369,7 @@
         <v>21</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>21</v>
@@ -31373,10 +31377,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31399,13 +31403,13 @@
         <v>21</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31491,10 +31495,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -31607,13 +31611,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D236" t="s" s="2">
         <v>21</v>
@@ -31635,13 +31639,13 @@
         <v>21</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -31727,10 +31731,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31753,13 +31757,13 @@
         <v>21</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -31810,7 +31814,7 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -31845,10 +31849,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31871,17 +31875,17 @@
         <v>21</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>21</v>
@@ -31930,7 +31934,7 @@
         <v>21</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -31939,16 +31943,16 @@
         <v>90</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="AM238" t="s" s="2">
         <v>153</v>
@@ -31957,7 +31961,7 @@
         <v>21</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="AP238" t="s" s="2">
         <v>21</v>
@@ -31965,10 +31969,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31994,10 +31998,10 @@
         <v>191</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -32048,7 +32052,7 @@
         <v>21</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -32066,7 +32070,7 @@
         <v>153</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="AM239" t="s" s="2">
         <v>153</v>
@@ -32083,10 +32087,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32112,16 +32116,16 @@
         <v>809</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>21</v>
@@ -32170,7 +32174,7 @@
         <v>21</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -32188,10 +32192,10 @@
         <v>21</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>21</v>
@@ -32205,10 +32209,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -32231,7 +32235,7 @@
         <v>21</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L241" t="s" s="2">
         <v>149</v>
@@ -32323,10 +32327,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32355,7 +32359,7 @@
         <v>157</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N242" t="s" s="2">
         <v>159</v>
@@ -32443,10 +32447,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -32481,7 +32485,7 @@
         <v>159</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>21</v>
@@ -32565,10 +32569,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -32594,16 +32598,16 @@
         <v>176</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>21</v>
@@ -32652,7 +32656,7 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>90</v>
@@ -32667,19 +32671,19 @@
         <v>102</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO244" t="s" s="2">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="AP244" t="s" s="2">
         <v>21</v>
@@ -32687,10 +32691,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32713,19 +32717,19 @@
         <v>21</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="O245" t="s" s="2">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>21</v>
@@ -32774,7 +32778,7 @@
         <v>21</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -32789,19 +32793,19 @@
         <v>102</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="AP245" t="s" s="2">
         <v>21</v>
@@ -32809,14 +32813,14 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
@@ -32835,16 +32839,16 @@
         <v>21</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -32894,7 +32898,7 @@
         <v>21</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -32909,10 +32913,10 @@
         <v>102</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="AM246" t="s" s="2">
         <v>153</v>
@@ -32921,7 +32925,7 @@
         <v>21</v>
       </c>
       <c r="AO246" t="s" s="2">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="AP246" t="s" s="2">
         <v>21</v>
@@ -32929,10 +32933,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32955,19 +32959,19 @@
         <v>91</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>21</v>
@@ -33016,7 +33020,7 @@
         <v>21</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -33031,13 +33035,13 @@
         <v>102</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>21</v>
@@ -33051,10 +33055,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -33080,16 +33084,16 @@
         <v>809</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="O248" t="s" s="2">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>21</v>
@@ -33138,7 +33142,7 @@
         <v>21</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -33156,7 +33160,7 @@
         <v>21</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="AM248" t="s" s="2">
         <v>153</v>
@@ -33173,10 +33177,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -33199,7 +33203,7 @@
         <v>21</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L249" t="s" s="2">
         <v>149</v>
@@ -33291,10 +33295,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -33323,7 +33327,7 @@
         <v>157</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N250" t="s" s="2">
         <v>159</v>
@@ -33411,10 +33415,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -33449,7 +33453,7 @@
         <v>159</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>21</v>
@@ -33533,10 +33537,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -33559,16 +33563,16 @@
         <v>91</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
@@ -33618,7 +33622,7 @@
         <v>21</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>90</v>
@@ -33636,7 +33640,7 @@
         <v>153</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AM252" t="s" s="2">
         <v>153</v>
@@ -33645,7 +33649,7 @@
         <v>21</v>
       </c>
       <c r="AO252" t="s" s="2">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="AP252" t="s" s="2">
         <v>21</v>
@@ -33653,10 +33657,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -33682,10 +33686,10 @@
         <v>110</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -33712,31 +33716,31 @@
         <v>21</v>
       </c>
       <c r="X253" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Y253" t="s" s="2">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="Z253" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="AA253" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB253" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC253" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD253" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE253" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF253" t="s" s="2">
         <v>986</v>
-      </c>
-      <c r="AA253" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB253" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC253" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD253" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE253" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF253" t="s" s="2">
-        <v>983</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>90</v>
@@ -33754,7 +33758,7 @@
         <v>153</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="AM253" t="s" s="2">
         <v>153</v>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T15:19:00+00:00</t>
+    <t>2025-01-24T15:25:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:25:06+00:00</t>
+    <t>2025-01-27T07:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T07:42:42+00:00</t>
+    <t>2025-01-27T10:22:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T10:22:54+00:00</t>
+    <t>2025-01-27T12:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:57:38+00:00</t>
+    <t>2026-08-11T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -697,7 +697,7 @@
     <t>Patient.extension:birthPlace.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1876,7 +1876,7 @@
     <t>AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -2057,7 +2057,7 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode}
 </t>
   </si>
   <si>
@@ -2241,7 +2241,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation}
 </t>
   </si>
   <si>

--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T12:53:53+00:00</t>
+    <t>2026-08-20T09:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>82</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>90</v>
